--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486791_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486791_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4908</v>
+        <v>2.8738</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9858</v>
+        <v>4.0272</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.495</v>
+        <v>-1.1534</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0764</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6697</v>
+        <v>1.7996</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7461</v>
+        <v>-2.4483</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6074</v>
+        <v>3.7461</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5668</v>
+        <v>3.2487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0407</v>
+        <v>0.4975</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6838</v>
+        <v>-4.3948</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.897</v>
+        <v>-1.4491</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-2.9458</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1585</v>
+        <v>2.7031</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3169</v>
+        <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6364</v>
+        <v>0.2482</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5368</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.3452</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2277</v>
+        <v>0.5712</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2657</v>
+        <v>2.3351</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2994</v>
+        <v>2.3245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9663</v>
+        <v>0.0106</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2729</v>
+        <v>1.2691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9105</v>
+        <v>1.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6375</v>
+        <v>-0.5109</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2114</v>
+        <v>1.7315</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0487</v>
+        <v>1.849</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1628</v>
+        <v>-0.1175</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9385</v>
+        <v>-0.4624</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1382</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8003</v>
+        <v>-0.3934</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7764</v>
+        <v>0.1586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9375</v>
+        <v>-0.0208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8389</v>
+        <v>0.1794</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9421</v>
+        <v>0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6565</v>
+        <v>0.6138</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2856</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1.2479</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0143</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0142</v>
+        <v>0.569</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2691</v>
+        <v>0.2729</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78</v>
+        <v>0.9105</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5109</v>
+        <v>-0.6375</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7315</v>
+        <v>1.2114</v>
       </c>
       <c r="K4" t="n">
-        <v>1.849</v>
+        <v>1.0487</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1175</v>
+        <v>0.1628</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4624</v>
+        <v>-0.9385</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.1382</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3934</v>
+        <v>-0.8003</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1765</v>
+        <v>0.7585</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3311</v>
+        <v>0.317</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1546</v>
+        <v>0.4416</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3282</v>
+        <v>-0.9421</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>-0.6565</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2856</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4119</v>
+        <v>0.8334</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9378</v>
+        <v>1.1794</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5259</v>
+        <v>-0.346</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.0764</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7996</v>
+        <v>0.6697</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.4483</v>
+        <v>-0.7461</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7461</v>
+        <v>1.6074</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2487</v>
+        <v>1.5668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4975</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.3948</v>
+        <v>-1.6838</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4491</v>
+        <v>-0.897</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9458</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7031</v>
+        <v>1.1585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8962</v>
+        <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2137</v>
+        <v>0.979</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1865</v>
+        <v>0.7304</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0272</v>
+        <v>0.2486</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5712</v>
+        <v>-1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.487</v>
+        <v>-0.4622</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2207</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2663</v>
+        <v>-0.2415</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4759</v>
@@ -922,13 +922,13 @@
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2042</v>
+        <v>-0.1793</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8692</v>
+        <v>-0.9644</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1035</v>
+        <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7657</v>
+        <v>-0.9643</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5037</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.022</v>
+        <v>-0.1172</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1436</v>
+        <v>-0.0551</v>
       </c>
       <c r="V7" t="n">
         <v>0.6565</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2597</v>
+        <v>-3.097</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9027</v>
+        <v>-2.6407</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.357</v>
+        <v>-0.4563</v>
       </c>
       <c r="G8" t="n">
         <v>-3.2959</v>
@@ -1078,13 +1078,13 @@
         <v>1.9308</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4303</v>
+        <v>0.593</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0555</v>
+        <v>0.2065</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4858</v>
+        <v>0.3865</v>
       </c>
       <c r="V8" t="n">
         <v>0.5712</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1107</v>
+        <v>-4.1604</v>
       </c>
       <c r="E9" t="n">
         <v>-1.0943</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0164</v>
+        <v>-3.0661</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5759</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3807</v>
+        <v>0.331</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1383</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5189</v>
+        <v>0.4693</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3709</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3293</v>
+        <v>-4.972</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1279</v>
+        <v>-2.9693</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2014</v>
+        <v>-2.0027</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6145</v>
@@ -1234,13 +1234,13 @@
         <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3367</v>
+        <v>0.0206</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0555</v>
+        <v>0.1031</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2811</v>
+        <v>-0.0825</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4128</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8865</v>
+        <v>-6.1322</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7692</v>
+        <v>-4.99</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1173</v>
+        <v>-1.1422</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8331</v>
@@ -1312,13 +1312,13 @@
         <v>2.7031</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0647</v>
+        <v>-0.3104</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1865</v>
+        <v>-0.4073</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1218</v>
+        <v>0.097</v>
       </c>
       <c r="V11" t="n">
         <v>0.3282</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.774</v>
+        <v>-12.498</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.981</v>
+        <v>-3.705000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.792899999999999</v>
+        <v>-8.792900000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-12.4821</v>
@@ -1390,13 +1390,13 @@
         <v>15.4462</v>
       </c>
       <c r="S12" t="n">
-        <v>2.206</v>
+        <v>2.482</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1346999999999998</v>
+        <v>0.4107000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0715</v>
+        <v>2.0714</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4982</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.07</v>
+        <v>7.1857</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2203</v>
+        <v>4.1168</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8498</v>
+        <v>3.0689</v>
       </c>
       <c r="G13" t="n">
         <v>5.89</v>
@@ -1468,13 +1468,13 @@
         <v>2.8962</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7327</v>
+        <v>0.8484</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0557</v>
+        <v>-0.1591</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7883</v>
+        <v>1.0074</v>
       </c>
       <c r="V13" t="n">
         <v>1.7989</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4476</v>
+        <v>4.0199</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6973</v>
+        <v>3.0075</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7504</v>
+        <v>1.0124</v>
       </c>
       <c r="G14" t="n">
         <v>3.1479</v>
@@ -1546,13 +1546,13 @@
         <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5997</v>
+        <v>-1.0274</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.6831</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.3443</v>
       </c>
       <c r="V14" t="n">
         <v>1.5133</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>I. SOTO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7152</v>
+        <v>3.1366</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6476</v>
+        <v>2.6987</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.4378</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0611</v>
+        <v>4.2466</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5386</v>
+        <v>1.8481</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5997</v>
+        <v>2.3986</v>
       </c>
       <c r="J15" t="n">
-        <v>4.311</v>
+        <v>4.0337</v>
       </c>
       <c r="K15" t="n">
-        <v>2.152</v>
+        <v>1.9177</v>
       </c>
       <c r="L15" t="n">
-        <v>2.159</v>
+        <v>2.116</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2499</v>
+        <v>0.2129</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6906</v>
+        <v>-0.0697</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4408</v>
+        <v>0.2826</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.9654</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.3515</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.3169</v>
-      </c>
       <c r="S15" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.1447</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.883</v>
+        <v>0.3101</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0005</v>
+        <v>-0.4548</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. SOTO RODRIGUEZ</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5531</v>
+        <v>3.0599</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3884</v>
+        <v>2.8545</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1647</v>
+        <v>0.2054</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2466</v>
+        <v>2.0611</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8481</v>
+        <v>-0.5386</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3986</v>
+        <v>2.5997</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0337</v>
+        <v>4.311</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9177</v>
+        <v>2.152</v>
       </c>
       <c r="L16" t="n">
-        <v>2.116</v>
+        <v>2.159</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2129</v>
+        <v>-2.2499</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0697</v>
+        <v>-2.6906</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2826</v>
+        <v>0.4408</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9654</v>
+        <v>0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-1.3515</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7281</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0001</v>
+        <v>-0.6762</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.728</v>
+        <v>0.1384</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5685</v>
+        <v>1.2541</v>
       </c>
       <c r="E17" t="n">
-        <v>1.464</v>
+        <v>1.0503</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1045</v>
+        <v>0.2038</v>
       </c>
       <c r="G17" t="n">
         <v>1.0432</v>
@@ -1780,13 +1780,13 @@
         <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6178</v>
+        <v>0.3034</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7722</v>
+        <v>0.3585</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1544</v>
+        <v>-0.0551</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4698</v>
+        <v>0.7759</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7657</v>
+        <v>0.9725</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2959</v>
+        <v>-0.1966</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2449</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.513</v>
+        <v>-0.2068</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3587</v>
+        <v>-0.1519</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1543</v>
+        <v>-0.0549</v>
       </c>
       <c r="V18" t="n">
         <v>1.2277</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0675</v>
+        <v>0.1172</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0345</v>
       </c>
       <c r="F19" t="n">
-        <v>0.102</v>
+        <v>0.1516</v>
       </c>
       <c r="G19" t="n">
         <v>0.0896</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0221</v>
+        <v>0.0276</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1189</v>
+        <v>-0.1133</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0713</v>
+        <v>-0.2781</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0476</v>
+        <v>0.1648</v>
       </c>
       <c r="G20" t="n">
         <v>0.4384</v>
@@ -2014,13 +2014,13 @@
         <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4082</v>
+        <v>0.4137</v>
       </c>
       <c r="T20" t="n">
-        <v>0.579</v>
+        <v>0.3722</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1708</v>
+        <v>0.0416</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3026</v>
+        <v>-1.8901</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5427</v>
+        <v>-1.9564</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2401</v>
+        <v>0.0663</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9298</v>
@@ -2092,13 +2092,13 @@
         <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3256</v>
+        <v>-0.2619</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1107</v>
+        <v>-0.5244</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4363</v>
+        <v>0.2625</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4707</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6963</v>
+        <v>-4.0825</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7418</v>
+        <v>-3.6384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9545</v>
+        <v>-0.4441</v>
       </c>
       <c r="G22" t="n">
         <v>-3.26</v>
@@ -2170,13 +2170,13 @@
         <v>2.3169</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5448</v>
+        <v>-0.931</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9657</v>
+        <v>-0.8623</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.0687</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8568</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.7739</v>
+        <v>13.4634</v>
       </c>
       <c r="E23" t="n">
-        <v>8.793000000000001</v>
+        <v>8.792899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>3.981100000000001</v>
+        <v>4.670300000000001</v>
       </c>
       <c r="G23" t="n">
         <v>12.4821</v>
@@ -2248,13 +2248,13 @@
         <v>15.4462</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.206</v>
+        <v>-1.5165</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.0713</v>
+        <v>-2.0714</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1348</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>2.498</v>
